--- a/data/nma/ARR_restricted.xlsx
+++ b/data/nma/ARR_restricted.xlsx
@@ -5618,8 +5618,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1dd74ed78a59e353fa0bdc00cb9d4ef2">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29b19980e720fd97176dcdbc89cda831" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACE3D2A8E3060445845CB33F649944D9" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="904d962808a52fea145147f501824070">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a4e98822-f433-4c96-8830-5cb2d7491f7d" xmlns:ns3="adc125f1-7df9-46f4-a9a7-022dd426a2bb" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea18719b0589a0490468c8ade8a27c2" ns2:_="" ns3:_="">
     <xsd:import namespace="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
     <xsd:import namespace="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
     <xsd:element name="properties">
@@ -5847,22 +5847,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DA09F2C-240B-49C8-BD9B-86660A6EC0F3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a4e98822-f433-4c96-8830-5cb2d7491f7d"/>
-    <ds:schemaRef ds:uri="adc125f1-7df9-46f4-a9a7-022dd426a2bb"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A86FE7D-63B4-4500-A5A4-DB9A1C067D6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
